--- a/光伏配储项目/电价数据/2026/鲘门站.xlsx
+++ b/光伏配储项目/电价数据/2026/鲘门站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.62033</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.82997</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.69777</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6069600000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6103</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43933</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43451</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43166</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41117</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42682</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45547</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51664</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.19524</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.21582</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27597</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21079</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17026</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.19622</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25156</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06161</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15907</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24167</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24047</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24529</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22973</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.88034</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.21931</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.51035</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.52588</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.53767</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6175700000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.63309</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7262000000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.24929</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43488</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65454</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9643699999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.30616</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.43993</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17275</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.30217</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.3806</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.56831</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.54389</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7841900000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.83635</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.34769</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.14053</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86537</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79362</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75363</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46473</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42387</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7003400000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74464</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86242</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9033099999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48911</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.50718</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49678</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49697</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47961</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46223</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.70345</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.56264</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.66203</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42887</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5093</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41414</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.57789</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85273</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.06785</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5805800000000001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.93432</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.88846</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.55699</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.83517</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.24093</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05645</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5007200000000001</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58421</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5437000000000001</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.53771</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8639</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6060800000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.78224</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.87162</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.2346</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.16011</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.89419</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.28493</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.1891</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.34761</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.12917</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.17382</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.73242</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.06468</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.89361</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.08077</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.00293</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.09447</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.8968200000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44692</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81249</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8323400000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44629</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44088</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33432</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50247</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4802</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42393</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4387799999999999</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46727</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44139</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.21015</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.26355</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26316</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.16191</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.53415</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.48582</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.48072</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.56625</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.57372</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.6589299999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.62385</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.89779</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.57784</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.69589</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.77574</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.52055</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.77838</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.71289</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64388</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63434</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49973</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50257</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5111600000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57701</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.61052</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.57777</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.59938</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23433</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61007</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.77161</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4727</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51239</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57775</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.73546</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.91031</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48405</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.61419</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.47498</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5752999999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.7413</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56236</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9012</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.70926</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.57726</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.51289</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64478</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45413</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34161</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5141699999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44516</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.48408</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.40861</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.49078</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.42948</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.65526</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.49641</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.50524</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.41607</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.21436</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.41757</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.59169</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48957</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.43121</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.45104</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.42619</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.50471</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.7056399999999999</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48224</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.4695299999999999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.53238</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6848200000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.54423</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.7644500000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.58677</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.54589</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.50276</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.47687</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30956</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24247</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14648</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.07379000000000001</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24377</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.25755</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.18135</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24516</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.27047</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22326</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08456</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.17834</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.13816</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01418</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26467</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4568</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.33083</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.45709</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.24847</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21551</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.10438</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22491</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.26345</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24501</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.23394</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10344</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04398</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01178</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20956</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28037</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1957</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.19062</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.06014</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06371</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06193</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3237</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30078</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45239</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7849400000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8718899999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.7637</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.61181</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44874</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.50541</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.56088</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6543099999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.86925</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.49665</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.70123</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.45809</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83423</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.51057</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57723</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.55126</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.23423</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33564</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9054500000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23484</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19432</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27497</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24569</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26268</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24819</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28421</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.41043</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26295</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81174</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38382</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08381</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6533300000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.74224</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46417</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4680299999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.23218</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26854</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46964</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.06812</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24451</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14557</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27323</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02855</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25482</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24598</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.48687</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.67325</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27455</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22677</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23823</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.24442</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.23399</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.24096</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21703</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25772</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.20874</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.20925</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28691</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.10109</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22729</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.10229</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.25255</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26775</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.25334</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.22454</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.16277</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20602</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22384</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23707</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24243</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.25359</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.26355</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22601</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.23223</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.25367</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.25064</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24592</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22609</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.24747</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.25424</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.23242</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26913</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24695</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42682</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30839</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.27842</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23798</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.42004</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.4814</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.47556</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44628</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.5519500000000001</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.48589</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32733</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.44923</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.24388</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.50188</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7726900000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.58438</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.56425</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.45633</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.53311</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5974299999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.47173</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.51459</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.47285</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.72093</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.53562</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.5639700000000001</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.44557</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.90387</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.6543099999999999</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.51381</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.61085</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.56724</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.5528500000000001</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.7465599999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.55459</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.5666</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.58396</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.51422</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.63082</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.46264</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.48353</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.7410599999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.56445</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.49738</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.77571</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.47288</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.47635</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22452</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.19533</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.25135</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.25709</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24613</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24865</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.24612</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.22248</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26922</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.24585</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.25111</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.26128</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.23994</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22856</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26686</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28261</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.43896</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.23474</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33154</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.13327</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6405700000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.9616</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31574</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.55575</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.55483</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.48344</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.52025</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.55453</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.75759</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.6313500000000001</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.72329</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6808099999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.78088</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46972</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.86758</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48085</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7731</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.70561</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.56675</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.47763</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.6039500000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.52458</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33248</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.43712</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48602</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.48229</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.48102</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.50684</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.52855</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.56541</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6636599999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.64442</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.44883</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.45163</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.7001900000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.89728</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.46698</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.45744</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.47224</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.52452</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.61191</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.45257</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.5312100000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5184099999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.47687</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5413600000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75546</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6075199999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65443</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.37729</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40634</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.14831</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.6424299999999999</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.55142</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.47785</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.45596</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47985</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.53366</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.23703</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27298</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27392</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27913</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26799</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25737</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26719</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.24215</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23974</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.14827</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.13755</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23979</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.13217</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25806</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23874</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.13101</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22588</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.23204</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.25322</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22878</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23602</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.12687</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.23964</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.12634</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.11121</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.25415</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23585</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.2159</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.10289</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11943</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27461</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24858</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.02296</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.19158</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27084</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01752</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24545</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25058</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25601</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25902</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.23455</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.23349</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.27332</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.15714</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23954</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23582</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24481</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25897</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.14187</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.10855</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.1168</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.11678</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.11494</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.11494</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.11605</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23993</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.10644</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.11494</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.11511</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22937</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.10863</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.10853</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.11954</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07723999999999999</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25598</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.12063</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00016</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04084</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02932</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00092</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02227</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03638</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19969</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.11791</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.3012</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.53942</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.48228</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.22184</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.24336</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23802</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23862</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.12178</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.23464</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22016</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12488</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.08952</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.10758</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.11668</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.13177</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.09705</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.14197</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.14896</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.16188</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42613</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.11637</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.57762</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8681</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85817</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10922</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.10674</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27384</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.14899</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.09545000000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28293</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00088</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00048</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.1129</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.66777</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.56909</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.6085499999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.09224</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97523</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.5772999999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.7308</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.62313</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8292200000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8335</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93124</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.56648</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6191599999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.57386</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33582</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.47607</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.27489</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48282</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26769</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.26225</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.24219</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25689</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.23483</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23834</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.12401</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.25137</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.26194</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25709</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.56726</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42155</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32188</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.47838</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7062999999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.45646</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46909</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.47764</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.57317</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.45974</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47476</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.82965</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8663099999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.28491</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.51328</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.60346</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.59126</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.17525</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.90718</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.57029</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64904</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.49136</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.41899</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45135</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.48702</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22321</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34005</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43552</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.47739</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50424</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.60522</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.39497</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.13263</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.64971</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.9392</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53111</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.67737</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.58066</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45711</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.82952</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.75209</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.9982000000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.90135</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.8119500000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.72415</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.48328</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34451</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.13837</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.5364500000000001</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.48291</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.5306900000000001</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.90937</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.54288</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.46998</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.22813</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.68121</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.45885</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.93208</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.56821</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.45357</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.51002</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.44812</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.43488</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.52012</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.47573</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.71861</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.49408</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.7127100000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.48961</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.52397</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.92253</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.4998</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.52667</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49958</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5297799999999999</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.40755</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.51112</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.52073</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.42865</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.54112</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.6324500000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.51649</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.48212</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.48285</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.46776</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35146</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17582</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14326</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04575</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12094</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22507</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14753</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14405</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19209</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22643</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15168</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15396</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19575</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14037</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.5306799999999999</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.59302</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45731</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37876</v>
       </c>
     </row>
   </sheetData>
